--- a/ig/mc-add-link-doc/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
     <t>Numéro de carte du professionnel.</t>
   </si>
   <si>
-    <t>Données descriptives du moyen d’identification des personnes physiques via une carte de professionnel.</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les informations de la carte CPx utilisée comme moyen d’identification des personnes physiques.</t>
   </si>
   <si>
     <t>Synonyme MOS : CarteProfessionnel</t>
